--- a/data/controles_results/dif_medias/dep_vars/ddifmedias_dep_vars_2017_T4_0.xlsx
+++ b/data/controles_results/dif_medias/dep_vars/ddifmedias_dep_vars_2017_T4_0.xlsx
@@ -57,7 +57,7 @@
     <t>N</t>
   </si>
   <si>
-    <t>91</t>
+    <t>87</t>
   </si>
   <si>
     <t xml:space="preserve"> (1) </t>
@@ -69,64 +69,64 @@
     <t>Mean/(SE)</t>
   </si>
   <si>
-    <t>6.329</t>
-  </si>
-  <si>
-    <t>(4.666)</t>
-  </si>
-  <si>
-    <t>7.659</t>
-  </si>
-  <si>
-    <t>(0.882)</t>
-  </si>
-  <si>
-    <t>75.352</t>
-  </si>
-  <si>
-    <t>(17.709)</t>
-  </si>
-  <si>
-    <t>90.240</t>
-  </si>
-  <si>
-    <t>(23.491)</t>
-  </si>
-  <si>
-    <t>1.379</t>
-  </si>
-  <si>
-    <t>(0.212)</t>
-  </si>
-  <si>
-    <t>7.319</t>
-  </si>
-  <si>
-    <t>(0.770)</t>
-  </si>
-  <si>
-    <t>4.344</t>
-  </si>
-  <si>
-    <t>(1.340)</t>
-  </si>
-  <si>
-    <t>2.837</t>
-  </si>
-  <si>
-    <t>(2.334)</t>
-  </si>
-  <si>
-    <t>103.647</t>
-  </si>
-  <si>
-    <t>(28.922)</t>
-  </si>
-  <si>
-    <t>78.905</t>
-  </si>
-  <si>
-    <t>(19.499)</t>
+    <t>1.729</t>
+  </si>
+  <si>
+    <t>(0.294)</t>
+  </si>
+  <si>
+    <t>7.989</t>
+  </si>
+  <si>
+    <t>(0.907)</t>
+  </si>
+  <si>
+    <t>57.158</t>
+  </si>
+  <si>
+    <t>(11.642)</t>
+  </si>
+  <si>
+    <t>64.988</t>
+  </si>
+  <si>
+    <t>(13.273)</t>
+  </si>
+  <si>
+    <t>1.259</t>
+  </si>
+  <si>
+    <t>(0.168)</t>
+  </si>
+  <si>
+    <t>7.598</t>
+  </si>
+  <si>
+    <t>(0.792)</t>
+  </si>
+  <si>
+    <t>4.322</t>
+  </si>
+  <si>
+    <t>(1.390)</t>
+  </si>
+  <si>
+    <t>0.521</t>
+  </si>
+  <si>
+    <t>(0.090)</t>
+  </si>
+  <si>
+    <t>74.235</t>
+  </si>
+  <si>
+    <t>(14.586)</t>
+  </si>
+  <si>
+    <t>57.955</t>
+  </si>
+  <si>
+    <t>(12.697)</t>
   </si>
   <si>
     <t>23</t>
@@ -198,7 +198,7 @@
     <t>(32.811)</t>
   </si>
   <si>
-    <t>114</t>
+    <t>110</t>
   </si>
   <si>
     <t>(2)-(1)</t>
@@ -210,34 +210,34 @@
     <t>Mean difference</t>
   </si>
   <si>
-    <t>-3.914</t>
-  </si>
-  <si>
-    <t>0.210</t>
-  </si>
-  <si>
-    <t>62.601</t>
-  </si>
-  <si>
-    <t>55.447</t>
-  </si>
-  <si>
-    <t>0.362</t>
-  </si>
-  <si>
-    <t>0.203</t>
-  </si>
-  <si>
-    <t>-1.375</t>
-  </si>
-  <si>
-    <t>-2.227</t>
-  </si>
-  <si>
-    <t>58.350</t>
-  </si>
-  <si>
-    <t>52.278</t>
+    <t>0.686</t>
+  </si>
+  <si>
+    <t>-0.119</t>
+  </si>
+  <si>
+    <t>80.795***</t>
+  </si>
+  <si>
+    <t>80.699**</t>
+  </si>
+  <si>
+    <t>0.482</t>
+  </si>
+  <si>
+    <t>-0.076</t>
+  </si>
+  <si>
+    <t>-1.353</t>
+  </si>
+  <si>
+    <t>0.088</t>
+  </si>
+  <si>
+    <t>87.762**</t>
+  </si>
+  <si>
+    <t>73.227**</t>
   </si>
 </sst>
 </file>
